--- a/public/uploads/employee.xlsx
+++ b/public/uploads/employee.xlsx
@@ -4,12 +4,11 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView activeTab="2" autoFilterDateGrouping="true" firstSheet="0" minimized="false" showHorizontalScroll="true" showSheetTabs="true" showVerticalScroll="true" tabRatio="600" visibility="visible"/>
+    <workbookView activeTab="0" autoFilterDateGrouping="true" firstSheet="0" minimized="false" showHorizontalScroll="true" showSheetTabs="true" showVerticalScroll="true" tabRatio="600" visibility="visible"/>
   </bookViews>
   <sheets>
     <sheet name="Employees" sheetId="1" r:id="rId4"/>
     <sheet name="Absences" sheetId="2" r:id="rId5"/>
-    <sheet name="Worksheet" sheetId="3" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
@@ -706,18 +705,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xml:space="preserve" mc:Ignorable="x14ac">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
-  <sheetData/>
-  <printOptions gridLines="false" gridLinesSet="true"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
-</worksheet>
 </file>